--- a/docs/pension_data_combined_2026-08-13.xlsx
+++ b/docs/pension_data_combined_2026-08-13.xlsx
@@ -1281,6 +1281,9 @@
       <c r="C51" t="n">
         <v>2.2436</v>
       </c>
+      <c r="D51" t="n">
+        <v>358440296.9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">

--- a/docs/pension_data_combined_2026-08-13.xlsx
+++ b/docs/pension_data_combined_2026-08-13.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.18</v>
-      </c>
       <c r="D48" t="n">
         <v>3913066.74</v>
       </c>
@@ -1349,9 +1346,6 @@
         <is>
           <t>2026-08-13</t>
         </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.2118</v>
       </c>
       <c r="D55" t="n">
         <v>60849589.83</v>

--- a/docs/pension_data_combined_2026-08-13.xlsx
+++ b/docs/pension_data_combined_2026-08-13.xlsx
@@ -1224,6 +1224,9 @@
           <t>2026-08-13</t>
         </is>
       </c>
+      <c r="C48" t="n">
+        <v>1.18</v>
+      </c>
       <c r="D48" t="n">
         <v>3913066.74</v>
       </c>
@@ -1346,6 +1349,9 @@
         <is>
           <t>2026-08-13</t>
         </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1.2118</v>
       </c>
       <c r="D55" t="n">
         <v>60849589.83</v>
